--- a/etf_holdings/2026-10-08_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2585</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.13%11,464,000</t>
+          <t>10.35%11,824,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.13%</t>
+          <t>10.35%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11464000</v>
+        <v>11824000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.75%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5950</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.46%4,650,000</t>
+          <t>9.58%4,650,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.58%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +630,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1305</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.61%19,300,000</t>
+          <t>8.19%5,086,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>8.19%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19300000</v>
+        <v>5086000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.73%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4835</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.41%5,086,000</t>
+          <t>8.16%18,721,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.41%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5086000</v>
+        <v>18721000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +761,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.8%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3545</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.35%6,062,000</t>
+          <t>7.16%6,062,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.35%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +824,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.88%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6805</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.82%2,502,000</t>
+          <t>6.16%2,502,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +887,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.52%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>647</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.20%23,519,000</t>
+          <t>5.13%23,519,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +950,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.93%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1990</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.03%7,389,000</t>
+          <t>4.99%7,389,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +1013,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.47%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5530</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.73%2,499,000</t>
+          <t>4.78%2,499,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.66%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1480</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.52%8,937,000</t>
+          <t>4.53%8,937,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.52%</t>
+          <t>4.53%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1139,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.71%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2015</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.32%6,264,000</t>
+          <t>4.45%6,264,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1202,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.68%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>148.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.04%79,618,000</t>
+          <t>4.03%79,618,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1265,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.99%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1720</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.80%6,467,000</t>
+          <t>3.86%6,467,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1328,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.18%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2240</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.31%4,315,561</t>
+          <t>3.32%4,315,561</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:54</t>
+          <t>2026-10-08 23:51:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1391,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.43%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2315</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.41%3,039,848</t>
+          <t>2.46%3,039,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,35 +1454,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.32%9,276,000</t>
+          <t>2.13%8,348,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>9276000</v>
+        <v>8348000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,35 +1517,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.78%616,000</t>
+          <t>1.96%684,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>616000</v>
+        <v>684000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,35 +1580,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.46%3,420,000</t>
+          <t>1.65%3,741,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3420000</v>
+        <v>3741000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1608,40 +1638,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>299.5</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.32%12,938,450</t>
+          <t>0.95%157,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>12938450</v>
+        <v>157900</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1671,40 +1701,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>304.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.96%157,900</t>
+          <t>0.88%8,456,450</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>157900</v>
+        <v>8456450</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,27 +1769,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.58%692,000</t>
+          <t>0.56%692,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1767,7 +1797,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1827,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+9.93%3320</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.27%476,000</t>
+          <t>0.29%251,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>476000</v>
+        <v>251000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1890,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.15%3020</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.26%251,000</t>
+          <t>0.28%476,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>251000</v>
+        <v>476000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1958,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.26%241.5</t>
+          <t>+1.66%245.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.66%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>241.5</t>
+          <t>245.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +2021,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.95%5520</t>
+          <t>+1.72%5615</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,7 +2049,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,17 +2084,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.47%872</t>
+          <t>+0.23%874</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2082,7 +2112,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2147,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.81%87.5</t>
+          <t>+0.46%87.9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2210,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.46%169</t>
+          <t>+0.3%169.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>169.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2208,7 +2238,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:55</t>
+          <t>2026-10-08 23:51:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2273,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2271,7 +2301,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2336,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>+0.81%248</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2332,7 +2362,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2458,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.63%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2519,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+7.05%250.5</t>
+          <t>-1%248</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>250.5</v>
+        <v>248</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2580,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.36%549</t>
+          <t>-2.55%535</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2641,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.24%4190</t>
+          <t>+3.7%4345</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2702,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.65%78.7</t>
+          <t>+2.41%80.6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.65%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>78.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2763,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.93%1230</t>
+          <t>-2.03%1205</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2824,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2885,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2946,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.45%335</t>
+          <t>-2.84%325.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +3007,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.94%579</t>
+          <t>-2.42%565</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3068,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3129,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.2%96.8</t>
+          <t>+1.65%98.4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>+1.65%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:56</t>
+          <t>2026-10-08 23:51:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3190,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2400</v>
+        <v>2330</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3251,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.83%1215</t>
+          <t>-7%1130</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1215</v>
+        <v>1130</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3312,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.89%568</t>
+          <t>-1.76%558</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3373,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.78%128.5</t>
+          <t>-0.39%128</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3434,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3495,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.52%190</t>
+          <t>-1.84%186.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>190</v>
+        <v>186.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:26:58</t>
+          <t>2026-10-08 23:51:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3556,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.42%178.5</t>
+          <t>-3.36%172.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>178.5</v>
+        <v>172.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
